--- a/artfynd/A 28401-2024 artfynd.xlsx
+++ b/artfynd/A 28401-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118732177</v>
       </c>
       <c r="B2" t="n">
-        <v>96801</v>
+        <v>96808</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28401-2024 artfynd.xlsx
+++ b/artfynd/A 28401-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,107 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131740062</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stubbkärr Nord, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>580152</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6398456</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28401-2024 artfynd.xlsx
+++ b/artfynd/A 28401-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>131740062</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28401-2024 artfynd.xlsx
+++ b/artfynd/A 28401-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>131740062</v>
       </c>
       <c r="B4" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28401-2024 artfynd.xlsx
+++ b/artfynd/A 28401-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>131740062</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28401-2024 artfynd.xlsx
+++ b/artfynd/A 28401-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>131740062</v>
       </c>
       <c r="B4" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28401-2024 artfynd.xlsx
+++ b/artfynd/A 28401-2024 artfynd.xlsx
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118732177</v>
+        <v>119054052</v>
       </c>
       <c r="B2" t="n">
-        <v>96813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580117</v>
+        <v>580121</v>
       </c>
       <c r="R2" t="n">
-        <v>6398416</v>
+        <v>6398344</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,22 +777,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119054052</v>
+        <v>131740062</v>
       </c>
       <c r="B3" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,32 +812,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 28401, Ankarsrum, Sm</t>
+          <t>Stubbkärr Nord, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580121</v>
+        <v>580152</v>
       </c>
       <c r="R3" t="n">
-        <v>6398344</v>
+        <v>6398456</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,57 +869,73 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist, Ingvor Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131740062</v>
+        <v>118732177</v>
       </c>
       <c r="B4" t="n">
-        <v>58109</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stubbkärr Nord, Sm</t>
+          <t>A 28401, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580152</v>
+        <v>580117</v>
       </c>
       <c r="R4" t="n">
-        <v>6398456</v>
+        <v>6398416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,25 +976,22 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
